--- a/data/trans_orig/P1415-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2012</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23386</t>
+          <t>23875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276876</t>
+          <t>277508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291014</t>
+          <t>290558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272814</t>
+          <t>274889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285386</t>
+          <t>286193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558597</t>
+          <t>558108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574519</t>
+          <t>574259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491208</t>
+          <t>491372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510427</t>
+          <t>509636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520753</t>
+          <t>520777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1008369</t>
+          <t>1007928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024198</t>
+          <t>1024138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318145</t>
+          <t>318473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332843</t>
+          <t>333004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340077</t>
+          <t>340081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654989</t>
+          <t>655035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664058</t>
+          <t>664067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360267</t>
+          <t>360823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371697</t>
+          <t>371617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375667</t>
+          <t>375972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387079</t>
+          <t>387052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742128</t>
+          <t>742327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756585</t>
+          <t>757729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202800</t>
+          <t>201741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211569</t>
+          <t>211573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211819</t>
+          <t>211611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218702</t>
+          <t>218697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417658</t>
+          <t>418630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429177</t>
+          <t>429216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262228</t>
+          <t>261867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271892</t>
+          <t>271851</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269230</t>
+          <t>269895</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277151</t>
+          <t>277144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535638</t>
+          <t>535758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547883</t>
+          <t>548035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>34889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635093</t>
+          <t>636132</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652294</t>
+          <t>653174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>681774</t>
+          <t>680956</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691733</t>
+          <t>691613</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1322244</t>
+          <t>1321752</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1342201</t>
+          <t>1342070</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760431</t>
+          <t>760585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775574</t>
+          <t>774759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>811338</t>
+          <t>811641</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821389</t>
+          <t>821444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1577030</t>
+          <t>1575783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1593199</t>
+          <t>1594182</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42583</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>76481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26002</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52895</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
+          <t>72883</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>116625</t>
+          <t>114447</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3350821</t>
+          <t>3350298</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3384196</t>
+          <t>3384042</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3502203</t>
+          <t>3504508</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3529096</t>
+          <t>3529767</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6865252</t>
+          <t>6867430</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6904795</t>
+          <t>6908994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2016</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288400</t>
+          <t>287380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273199</t>
+          <t>272911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284808</t>
+          <t>284867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564377</t>
+          <t>564445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576973</t>
+          <t>576806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496491</t>
+          <t>495595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513081</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521992</t>
+          <t>522001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1014020</t>
+          <t>1014079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023747</t>
+          <t>1023792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309509</t>
+          <t>307832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316817</t>
+          <t>316825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329386</t>
+          <t>329368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641917</t>
+          <t>641800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652138</t>
+          <t>652135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357388</t>
+          <t>358117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367978</t>
+          <t>368068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376270</t>
+          <t>376951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386090</t>
+          <t>386103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739434</t>
+          <t>740398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752660</t>
+          <t>752668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206682</t>
+          <t>205160</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209714</t>
+          <t>209028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217710</t>
+          <t>217706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419203</t>
+          <t>419144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428063</t>
+          <t>428065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258671</t>
+          <t>258786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259619</t>
+          <t>259701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270756</t>
+          <t>270227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522295</t>
+          <t>522668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533275</t>
+          <t>533300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20937</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29533</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>641367</t>
+          <t>641763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652777</t>
+          <t>653524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670357</t>
+          <t>671076</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685693</t>
+          <t>685681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318319</t>
+          <t>1318540</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1335828</t>
+          <t>1336456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>755770</t>
+          <t>757008</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771572</t>
+          <t>772047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>799824</t>
+          <t>800946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>816835</t>
+          <t>817715</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1562461</t>
+          <t>1563114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1584724</t>
+          <t>1585287</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48157</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42821</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>74023</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74075</t>
+          <t>74417</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114000</t>
+          <t>112707</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3346193</t>
+          <t>3346009</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3369196</t>
+          <t>3369276</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3472222</t>
+          <t>3470519</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3501721</t>
+          <t>3503149</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6824892</t>
+          <t>6826185</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6864817</t>
+          <t>6864475</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P1415-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277508</t>
+          <t>277615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290558</t>
+          <t>290794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274889</t>
+          <t>273526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286193</t>
+          <t>285386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558108</t>
+          <t>556694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574259</t>
+          <t>574610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491372</t>
+          <t>493035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509636</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520777</t>
+          <t>520747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007928</t>
+          <t>1007080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024138</t>
+          <t>1024185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318473</t>
+          <t>318916</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333004</t>
+          <t>333105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340081</t>
+          <t>340069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655035</t>
+          <t>655123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360823</t>
+          <t>359949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371617</t>
+          <t>371680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375972</t>
+          <t>377155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387052</t>
+          <t>387002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742327</t>
+          <t>741916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>757729</t>
+          <t>757613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201741</t>
+          <t>202057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211573</t>
+          <t>211583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211611</t>
+          <t>212294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218697</t>
+          <t>218722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418630</t>
+          <t>417515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429216</t>
+          <t>429109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261867</t>
+          <t>261599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271851</t>
+          <t>271806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269895</t>
+          <t>270351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277144</t>
+          <t>277150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535758</t>
+          <t>535173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548035</t>
+          <t>547866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>28438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>636132</t>
+          <t>634350</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653174</t>
+          <t>652816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680956</t>
+          <t>680525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691613</t>
+          <t>690869</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1321752</t>
+          <t>1321238</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1342070</t>
+          <t>1342105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25893</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760585</t>
+          <t>759722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774759</t>
+          <t>774784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>811641</t>
+          <t>811722</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821444</t>
+          <t>821510</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1575783</t>
+          <t>1577800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1594182</t>
+          <t>1594351</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76481</t>
+          <t>75389</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114447</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3350298</t>
+          <t>3351390</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3384042</t>
+          <t>3384422</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3504508</t>
+          <t>3501659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3529767</t>
+          <t>3527906</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6867430</t>
+          <t>6865324</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6908994</t>
+          <t>6906208</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287380</t>
+          <t>287800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272911</t>
+          <t>273508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284867</t>
+          <t>284854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564445</t>
+          <t>564430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576806</t>
+          <t>576835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>495595</t>
+          <t>496717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513269</t>
+          <t>512825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522001</t>
+          <t>521992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1014079</t>
+          <t>1014310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023792</t>
+          <t>1023693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307832</t>
+          <t>308646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316825</t>
+          <t>316804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329368</t>
+          <t>329719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641800</t>
+          <t>642683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652135</t>
+          <t>652132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358117</t>
+          <t>357758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368068</t>
+          <t>367955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376951</t>
+          <t>376983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386103</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>740398</t>
+          <t>739874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752668</t>
+          <t>753034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,47 +5476,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>4760</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>10463</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>4760</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1743</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10664</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205160</t>
+          <t>206102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209028</t>
+          <t>209424</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217706</t>
+          <t>217555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,47 +5589,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>425048</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>419345</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>428099</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,6%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>425048</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>419144</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>428065</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>14113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258786</t>
+          <t>259129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259701</t>
+          <t>260732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270227</t>
+          <t>271090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522668</t>
+          <t>522125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533300</t>
+          <t>533270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29312</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>641763</t>
+          <t>641741</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653524</t>
+          <t>652814</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671076</t>
+          <t>671773</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685681</t>
+          <t>685508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318540</t>
+          <t>1317024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1336456</t>
+          <t>1335773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>41635</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757008</t>
+          <t>754998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772047</t>
+          <t>771374</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>800946</t>
+          <t>800176</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817715</t>
+          <t>817999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1563114</t>
+          <t>1563115</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1585287</t>
+          <t>1585845</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48341</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41393</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74023</t>
+          <t>72730</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74417</t>
+          <t>74796</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>112707</t>
+          <t>112608</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3346009</t>
+          <t>3345196</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3369276</t>
+          <t>3370188</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3470519</t>
+          <t>3471812</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3503149</t>
+          <t>3501177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6826185</t>
+          <t>6826284</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6864475</t>
+          <t>6864096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
